--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137031742</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137031742</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137031742</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137031742</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137031742</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30907-2026 artfynd.xlsx
+++ b/artfynd/A 30907-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137031742</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
